--- a/Digital-Business-Toolkit/04-Collection/Product.xlsx
+++ b/Digital-Business-Toolkit/04-Collection/Product.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Main Workspace" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Quick Start" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="User Guide" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="לוח בקרה" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="שולחן עבודה" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="התחלה מהירה" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="מדריך שימוש" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,7 +658,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Payment &amp; Collection Manager — Dashboard</t>
+          <t>לוח בקרה — ניהול גבייה</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -669,7 +669,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — Get paid on time, every time</t>
+          <t>ContractorOS — קבלו תשלום בזמן, בכל פעם</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -706,42 +706,42 @@
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="B6" s="6">
-        <f>SUM('Main Workspace'!E4:E33)</f>
+        <f>SUM('שולחן עבודה'!E4:E33)</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>SUM('Main Workspace'!F4:F33)</f>
+        <f>SUM('שולחן עבודה'!F4:F33)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>SUM('Main Workspace'!G4:G33)</f>
+        <f>SUM('שולחן עבודה'!G4:G33)</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>COUNTIF('Main Workspace'!I4:I33,"באיחור")</f>
+        <f>COUNTIF('שולחן עבודה'!I4:I33,"באיחור")</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>IFERROR(SUM('Main Workspace'!F4:F33)/SUM('Main Workspace'!E4:E33),0)</f>
+        <f>IFERROR(SUM('שולחן עבודה'!F4:F33)/SUM('שולחן עבודה'!E4:E33),0)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>⚠ Business Insights / התראות</t>
+          <t>⚠ תובנות עסקיות והתראות</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="9">
-        <f>IF(COUNTIF('Main Workspace'!I4:I33,"באיחור")&gt;0,"יש "&amp;COUNTIF('Main Workspace'!I4:I33,"באיחור")&amp;" תשלומים באיחור — כדאי ליצור קשר עם הלקוחות.","אין תשלומים באיחור כרגע.")</f>
+        <f>IF(COUNTIF('שולחן עבודה'!I4:I33,"באיחור")&gt;0,"יש "&amp;COUNTIF('שולחן עבודה'!I4:I33,"באיחור")&amp;" תשלומים באיחור — כדאי ליצור קשר עם הלקוחות.","אין תשלומים באיחור כרגע.")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="10">
-        <f>IF(SUM('Main Workspace'!G4:G33)&gt;SUM('Main Workspace'!E4:E33)*0.3,"מעל 30% מהחיוב הכולל עדיין לא נגבה.","רמת הגבייה בטווח בריא.")</f>
+        <f>IF(SUM('שולחן עבודה'!G4:G33)&gt;SUM('שולחן עבודה'!E4:E33)*0.3,"מעל 30% מהחיוב הכולל עדיין לא נגבה.","רמת הגבייה בטווח בריא.")</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>ניהול גבייה | Payment &amp; Collection Manager</t>
+          <t>ניהול גבייה</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>פרויקט</t>
+          <t>שם פרויקט</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>התחלה מהירה | Quick Start</t>
+          <t>התחלה מהירה</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1559,7 +1559,7 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>1. עברו ללשונית 'Main Workspace'.</t>
+          <t>1. עברו ללשונית 'שולחן עבודה'.</t>
         </is>
       </c>
     </row>
@@ -1587,14 +1587,14 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>5. עברו ל-Dashboard לראות כמה עדיין צריך לגבות ומי באיחור.</t>
+          <t>5. עברו ל-לוח הבקרה לראות כמה עדיין צריך לגבות ומי באיחור.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>טיפ: בדקו את Dashboard פעם בשבוע ופנו מיידית ללקוחות שסומנו 'באיחור'.</t>
+          <t>טיפ: בדקו את לוח הבקרה פעם בשבוע ופנו מיידית ללקוחות שסומנו 'באיחור'.</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>מדריך שימוש | User Guide</t>
+          <t>מדריך שימוש</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1721,7 +1721,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>מה Dashboard מציג?</t>
+          <t>מה לוח הבקרה מציג?</t>
         </is>
       </c>
       <c r="C10" s="28" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="13">
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>שאלות נפוצות (FAQ)</t>
+          <t>שאלות נפוצות</t>
         </is>
       </c>
     </row>

--- a/Digital-Business-Toolkit/04-Collection/Product.xlsx
+++ b/Digital-Business-Toolkit/04-Collection/Product.xlsx
@@ -669,7 +669,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — קבלו תשלום בזמן, בכל פעם</t>
+          <t>JobMargin — קבלו תשלום בזמן, בכל פעם</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
